--- a/companies/alder-ridge/source-files/Shared/Operations/Commercial/CO Log/CO log MASTER (do not sort)_6.30.26 - PR copy.xlsx
+++ b/companies/alder-ridge/source-files/Shared/Operations/Commercial/CO Log/CO log MASTER (do not sort)_6.30.26 - PR copy.xlsx
@@ -870,7 +870,7 @@
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
-          <t>Close Treatment</t>
+          <t>Finance Review Status</t>
         </is>
       </c>
       <c r="K5" s="5" t="inlineStr">
@@ -920,7 +920,7 @@
       </c>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>Exclude from contract value; include $275k probable cost exposure in EAC</t>
+          <t>Pending controller assessment under signed WIP policy</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
@@ -970,7 +970,7 @@
       </c>
       <c r="J7" s="6" t="inlineStr">
         <is>
-          <t>Do not net the recovery against forecast cost</t>
+          <t>Pending controller assessment under signed WIP policy</t>
         </is>
       </c>
       <c r="K7" s="6" t="inlineStr">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>Exclude revenue; include $210k probable cost exposure</t>
+          <t>Pending controller assessment under signed WIP policy</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
@@ -1070,7 +1070,7 @@
       </c>
       <c r="J9" s="6" t="inlineStr">
         <is>
-          <t>Included in accounting-system approved change orders</t>
+          <t>Executed before cutoff</t>
         </is>
       </c>
       <c r="K9" s="6" t="inlineStr">
@@ -1120,7 +1120,7 @@
       </c>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>Exclude revenue; include $45k close-out cost exposure</t>
+          <t>Pending controller assessment under signed WIP policy</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="J11" s="6" t="inlineStr">
         <is>
-          <t>Exclude from June close</t>
+          <t>Pending controller assessment under signed WIP policy</t>
         </is>
       </c>
       <c r="K11" s="6" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>Already included in current contract and cost budget</t>
+          <t>Executed before cutoff</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J13" s="6" t="inlineStr">
         <is>
-          <t>Already included in current contract and cost budget</t>
+          <t>Executed before cutoff</t>
         </is>
       </c>
       <c r="K13" s="6" t="inlineStr">
